--- a/src/test/resources/state_counters_qa.xlsx
+++ b/src/test/resources/state_counters_qa.xlsx
@@ -487,8 +487,8 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
-        <v>9543</v>
+      <c r="B2" s="1" t="n">
+        <v>9550.0</v>
       </c>
       <c r="C2" s="1">
         <v>2285</v>
@@ -508,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>9038.0</v>
+        <v>9046.0</v>
       </c>
       <c r="C3" s="1">
         <v>2230</v>

--- a/src/test/resources/state_counters_qa.xlsx
+++ b/src/test/resources/state_counters_qa.xlsx
@@ -508,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>9046.0</v>
+        <v>9072.0</v>
       </c>
       <c r="C3" s="1">
         <v>2230</v>

--- a/src/test/resources/state_counters_qa.xlsx
+++ b/src/test/resources/state_counters_qa.xlsx
@@ -508,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>9072.0</v>
+        <v>9080.0</v>
       </c>
       <c r="C3" s="1">
         <v>2230</v>

--- a/src/test/resources/state_counters_qa.xlsx
+++ b/src/test/resources/state_counters_qa.xlsx
@@ -508,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>9080.0</v>
+        <v>9081.0</v>
       </c>
       <c r="C3" s="1">
         <v>2230</v>
